--- a/_producao-16-8 copy/_resultados.xlsx
+++ b/_producao-16-8 copy/_resultados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_producao-16-8 copy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C8851F-DAAF-4376-B2B9-68EC66A23830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD9CB2D-452C-4F2A-BDFD-6A9292123CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -287,6 +287,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -314,7 +315,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -622,10 +622,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -634,124 +634,124 @@
       <c r="D2" s="3">
         <v>1.22740707443255E-3</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="9">
         <f>AVERAGE(D2:D12)</f>
         <v>1.3405988398128117E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>1.5217850441141701E-3</v>
       </c>
-      <c r="E3" s="7"/>
+      <c r="E3" s="8"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>1.4187702239963399E-3</v>
       </c>
-      <c r="E4" s="7"/>
+      <c r="E4" s="8"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>1.21923057588587E-3</v>
       </c>
-      <c r="E5" s="7"/>
+      <c r="E5" s="8"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3">
         <v>1.2107251197056299E-3</v>
       </c>
-      <c r="E6" s="7"/>
+      <c r="E6" s="8"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
       <c r="D7" s="3">
         <v>1.5994412310248701E-3</v>
       </c>
-      <c r="E7" s="7"/>
+      <c r="E7" s="8"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="3">
         <v>1.3964272541872899E-3</v>
       </c>
-      <c r="E8" s="7"/>
+      <c r="E8" s="8"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
       <c r="D9" s="3">
         <v>1.5234914987065399E-3</v>
       </c>
-      <c r="E9" s="7"/>
+      <c r="E9" s="8"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3">
         <v>1.14432918115938E-3</v>
       </c>
-      <c r="E10" s="7"/>
+      <c r="E10" s="8"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
       <c r="D11" s="3">
         <v>1.29480134619695E-3</v>
       </c>
-      <c r="E11" s="7"/>
+      <c r="E11" s="8"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="3">
         <v>1.1901786885313401E-3</v>
       </c>
-      <c r="E12" s="7"/>
+      <c r="E12" s="8"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="9" t="s">
+      <c r="A13" s="8"/>
+      <c r="B13" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="1">
@@ -760,124 +760,124 @@
       <c r="D13" s="3">
         <v>1.76494351019696E-4</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="13">
         <f>AVERAGE(D13:D23)</f>
         <v>4.6044642516324585E-4</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="10"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="11"/>
       <c r="C14" s="1">
         <v>2</v>
       </c>
       <c r="D14" s="3">
         <v>5.46025356640438E-4</v>
       </c>
-      <c r="E14" s="13"/>
+      <c r="E14" s="14"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="7"/>
-      <c r="B15" s="10"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="11"/>
       <c r="C15" s="1">
         <v>3</v>
       </c>
       <c r="D15" s="3">
         <v>1.7489087688418899E-4</v>
       </c>
-      <c r="E15" s="13"/>
+      <c r="E15" s="14"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="10"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="11"/>
       <c r="C16" s="1">
         <v>4</v>
       </c>
       <c r="D16" s="3">
         <v>4.5331415788522699E-4</v>
       </c>
-      <c r="E16" s="13"/>
+      <c r="E16" s="14"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="10"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="11"/>
       <c r="C17" s="1">
         <v>5</v>
       </c>
       <c r="D17" s="3">
         <v>4.5224030226177498E-4</v>
       </c>
-      <c r="E17" s="13"/>
+      <c r="E17" s="14"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="7"/>
-      <c r="B18" s="10"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="11"/>
       <c r="C18" s="1">
         <v>6</v>
       </c>
       <c r="D18" s="3">
         <v>3.25042909349475E-4</v>
       </c>
-      <c r="E18" s="13"/>
+      <c r="E18" s="14"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="7"/>
-      <c r="B19" s="10"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="11"/>
       <c r="C19" s="1">
         <v>7</v>
       </c>
       <c r="D19" s="3">
         <v>5.4759582523591596E-4</v>
       </c>
-      <c r="E19" s="13"/>
+      <c r="E19" s="14"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="7"/>
-      <c r="B20" s="10"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="11"/>
       <c r="C20" s="1">
         <v>8</v>
       </c>
       <c r="D20" s="3">
         <v>4.0296400000000003E-5</v>
       </c>
-      <c r="E20" s="13"/>
+      <c r="E20" s="14"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="7"/>
-      <c r="B21" s="10"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="11"/>
       <c r="C21" s="1">
         <v>9</v>
       </c>
       <c r="D21" s="3">
         <v>8.9001901515576199E-4</v>
       </c>
-      <c r="E21" s="13"/>
+      <c r="E21" s="14"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="7"/>
-      <c r="B22" s="10"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="11"/>
       <c r="C22" s="1">
         <v>10</v>
       </c>
       <c r="D22" s="3">
         <v>8.6876944325313898E-4</v>
       </c>
-      <c r="E22" s="13"/>
+      <c r="E22" s="14"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="7"/>
-      <c r="B23" s="11"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="12"/>
       <c r="C23" s="1">
         <v>11</v>
       </c>
       <c r="D23" s="3">
         <v>5.9022203911008697E-4</v>
       </c>
-      <c r="E23" s="14"/>
+      <c r="E23" s="15"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7" t="s">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="1">
@@ -886,118 +886,118 @@
       <c r="D24" s="3">
         <v>1.73793482370665E-4</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="9">
         <f>AVERAGE(D24:D33)</f>
         <v>2.0032376576300951E-4</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
       <c r="C25" s="1">
         <v>2</v>
       </c>
       <c r="D25" s="3">
         <v>4.4079599999999997E-5</v>
       </c>
-      <c r="E25" s="7"/>
+      <c r="E25" s="8"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
       <c r="C26" s="1">
         <v>3</v>
       </c>
       <c r="D26" s="3">
         <v>1.9820721733818201E-4</v>
       </c>
-      <c r="E26" s="7"/>
+      <c r="E26" s="8"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
       <c r="C27" s="1">
         <v>4</v>
       </c>
       <c r="D27" s="3">
         <v>2.6898882604876098E-4</v>
       </c>
-      <c r="E27" s="7"/>
+      <c r="E27" s="8"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
       <c r="C28" s="1">
         <v>5</v>
       </c>
       <c r="D28" s="3">
         <v>9.9348000000000002E-6</v>
       </c>
-      <c r="E28" s="7"/>
+      <c r="E28" s="8"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
       <c r="C29" s="1">
         <v>6</v>
       </c>
       <c r="D29" s="3">
         <v>1.70899292234211E-4</v>
       </c>
-      <c r="E29" s="7"/>
+      <c r="E29" s="8"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
       <c r="C30" s="1">
         <v>7</v>
       </c>
       <c r="D30" s="3">
         <v>3.7644454634369102E-4</v>
       </c>
-      <c r="E30" s="7"/>
+      <c r="E30" s="8"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
       <c r="C31" s="1">
         <v>8</v>
       </c>
       <c r="D31" s="3">
         <v>7.5758852866904895E-5</v>
       </c>
-      <c r="E31" s="7"/>
+      <c r="E31" s="8"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
       <c r="C32" s="1">
         <v>9</v>
       </c>
       <c r="D32" s="3">
         <v>4.9271851899704603E-4</v>
       </c>
-      <c r="E32" s="7"/>
+      <c r="E32" s="8"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
       <c r="C33" s="1">
         <v>10</v>
       </c>
       <c r="D33" s="3">
         <v>1.9241252143063401E-4</v>
       </c>
-      <c r="E33" s="7"/>
+      <c r="E33" s="8"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1044,354 +1044,362 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="8">
+      <c r="E2" s="9">
         <f>AVERAGE(D2:D12)</f>
         <v>1.4591194330376932E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="6">
         <v>1.5217850441141701E-3</v>
       </c>
-      <c r="E3" s="7"/>
+      <c r="E3" s="8"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="6">
         <v>1.4187702239963399E-3</v>
       </c>
-      <c r="E4" s="7"/>
+      <c r="E4" s="8"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="7"/>
+      <c r="E5" s="8"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="7"/>
+      <c r="E6" s="8"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="6">
         <v>1.5994412310248701E-3</v>
       </c>
-      <c r="E7" s="7"/>
+      <c r="E7" s="8"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="6">
         <v>1.3964272541872899E-3</v>
       </c>
-      <c r="E8" s="7"/>
+      <c r="E8" s="8"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="6">
         <v>1.5234914987065399E-3</v>
       </c>
-      <c r="E9" s="7"/>
+      <c r="E9" s="8"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="7"/>
+      <c r="E10" s="8"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="6">
         <v>1.29480134619695E-3</v>
       </c>
-      <c r="E11" s="7"/>
+      <c r="E11" s="8"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="3"/>
-      <c r="E12" s="7"/>
+      <c r="E12" s="8"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="9" t="s">
+      <c r="A13" s="8"/>
+      <c r="B13" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="1">
         <v>1</v>
       </c>
       <c r="D13" s="3"/>
-      <c r="E13" s="12">
+      <c r="E13" s="13">
         <f>AVERAGE(D13:D23)</f>
         <v>6.4932430621342815E-4</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="10"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="11"/>
       <c r="C14" s="1">
         <v>2</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="6">
         <v>5.46025356640438E-4</v>
       </c>
-      <c r="E14" s="13"/>
+      <c r="E14" s="14"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="7"/>
-      <c r="B15" s="10"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="11"/>
       <c r="C15" s="1">
         <v>3</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="13"/>
+      <c r="E15" s="14"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="10"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="11"/>
       <c r="C16" s="1">
         <v>4</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="6">
         <v>4.5331415788522699E-4</v>
       </c>
-      <c r="E16" s="13"/>
+      <c r="E16" s="14"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="10"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="11"/>
       <c r="C17" s="1">
         <v>5</v>
       </c>
       <c r="D17" s="3"/>
-      <c r="E17" s="13"/>
+      <c r="E17" s="14"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="7"/>
-      <c r="B18" s="10"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="11"/>
       <c r="C18" s="1">
         <v>6</v>
       </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="13"/>
+      <c r="E18" s="14"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="7"/>
-      <c r="B19" s="10"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="11"/>
       <c r="C19" s="1">
         <v>7</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="6">
         <v>5.4759582523591596E-4</v>
       </c>
-      <c r="E19" s="13"/>
+      <c r="E19" s="14"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="7"/>
-      <c r="B20" s="10"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="11"/>
       <c r="C20" s="1">
         <v>8</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="13"/>
+      <c r="E20" s="14"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="7"/>
-      <c r="B21" s="10"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="11"/>
       <c r="C21" s="1">
         <v>9</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="6">
         <v>8.9001901515576199E-4</v>
       </c>
-      <c r="E21" s="13"/>
+      <c r="E21" s="14"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="7"/>
-      <c r="B22" s="10"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="11"/>
       <c r="C22" s="1">
         <v>10</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="6">
         <v>8.6876944325313898E-4</v>
       </c>
-      <c r="E22" s="13"/>
+      <c r="E22" s="14"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="7"/>
-      <c r="B23" s="11"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="12"/>
       <c r="C23" s="1">
         <v>11</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="6">
         <v>5.9022203911008697E-4</v>
       </c>
-      <c r="E23" s="14"/>
+      <c r="E23" s="15"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7" t="s">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="1">
         <v>1</v>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="6">
         <v>1.73793482370665E-4</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="9">
         <f>AVERAGE(D24:D33)</f>
-        <v>1.4252516104009948E-4</v>
+        <v>2.0032376576300951E-4</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
       <c r="C25" s="1">
         <v>2</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="3">
         <v>4.4079599999999997E-5</v>
       </c>
-      <c r="E25" s="7"/>
+      <c r="E25" s="8"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
       <c r="C26" s="1">
         <v>3</v>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="6">
         <v>1.9820721733818201E-4</v>
       </c>
-      <c r="E26" s="7"/>
+      <c r="E26" s="8"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
       <c r="C27" s="1">
         <v>4</v>
       </c>
-      <c r="D27" s="3"/>
-      <c r="E27" s="7"/>
+      <c r="D27" s="3">
+        <v>2.6898882604876098E-4</v>
+      </c>
+      <c r="E27" s="8"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
       <c r="C28" s="1">
         <v>5</v>
       </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="7"/>
+      <c r="D28" s="3">
+        <v>9.9348000000000002E-6</v>
+      </c>
+      <c r="E28" s="8"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
       <c r="C29" s="1">
         <v>6</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="6">
         <v>1.70899292234211E-4</v>
       </c>
-      <c r="E29" s="7"/>
+      <c r="E29" s="8"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
       <c r="C30" s="1">
         <v>7</v>
       </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="7"/>
+      <c r="D30" s="3">
+        <v>3.7644454634369102E-4</v>
+      </c>
+      <c r="E30" s="8"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
       <c r="C31" s="1">
         <v>8</v>
       </c>
-      <c r="D31" s="15">
+      <c r="D31" s="3">
         <v>7.5758852866904895E-5</v>
       </c>
-      <c r="E31" s="7"/>
+      <c r="E31" s="8"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
       <c r="C32" s="1">
         <v>9</v>
       </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="7"/>
+      <c r="D32" s="3">
+        <v>4.9271851899704603E-4</v>
+      </c>
+      <c r="E32" s="8"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
       <c r="C33" s="1">
         <v>10</v>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="6">
         <v>1.9241252143063401E-4</v>
       </c>
-      <c r="E33" s="7"/>
+      <c r="E33" s="8"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1438,10 +1446,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -1450,124 +1458,124 @@
       <c r="D2" s="3">
         <v>6.8494550335423199E-3</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="9">
         <f>AVERAGE(D2:D12)</f>
         <v>7.2093580443383567E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>7.7222014481316001E-3</v>
       </c>
-      <c r="E3" s="7"/>
+      <c r="E3" s="8"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>7.4276032951078701E-3</v>
       </c>
-      <c r="E4" s="7"/>
+      <c r="E4" s="8"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>6.9163642363323698E-3</v>
       </c>
-      <c r="E5" s="7"/>
+      <c r="E5" s="8"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3">
         <v>7.1247468487415202E-3</v>
       </c>
-      <c r="E6" s="7"/>
+      <c r="E6" s="8"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
       <c r="D7" s="3">
         <v>7.9683523176790998E-3</v>
       </c>
-      <c r="E7" s="7"/>
+      <c r="E7" s="8"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="3">
         <v>7.1325304703669396E-3</v>
       </c>
-      <c r="E8" s="7"/>
+      <c r="E8" s="8"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
       <c r="D9" s="3">
         <v>7.6723666731501597E-3</v>
       </c>
-      <c r="E9" s="7"/>
+      <c r="E9" s="8"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3">
         <v>6.44864466466859E-3</v>
       </c>
-      <c r="E10" s="7"/>
+      <c r="E10" s="8"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
       <c r="D11" s="3">
         <v>7.1998086663083299E-3</v>
       </c>
-      <c r="E11" s="7"/>
+      <c r="E11" s="8"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="3">
         <v>6.8408648336931201E-3</v>
       </c>
-      <c r="E12" s="7"/>
+      <c r="E12" s="8"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7" t="s">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="1">
@@ -1576,124 +1584,124 @@
       <c r="D13" s="3">
         <v>4.4059430113216501E-3</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="9">
         <f>AVERAGE(D13:D23)</f>
         <v>5.6171193080640424E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
       <c r="C14" s="1">
         <v>2</v>
       </c>
       <c r="D14" s="3">
         <v>6.0285373262784596E-3</v>
       </c>
-      <c r="E14" s="7"/>
+      <c r="E14" s="8"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
       <c r="C15" s="1">
         <v>3</v>
       </c>
       <c r="D15" s="3">
         <v>4.6542086132795998E-3</v>
       </c>
-      <c r="E15" s="7"/>
+      <c r="E15" s="8"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
       <c r="C16" s="1">
         <v>4</v>
       </c>
       <c r="D16" s="3">
         <v>5.4842343524997596E-3</v>
       </c>
-      <c r="E16" s="7"/>
+      <c r="E16" s="8"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
       <c r="C17" s="1">
         <v>5</v>
       </c>
       <c r="D17" s="3">
         <v>5.2386490268761304E-3</v>
       </c>
-      <c r="E17" s="7"/>
+      <c r="E17" s="8"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
       <c r="C18" s="1">
         <v>6</v>
       </c>
       <c r="D18" s="3">
         <v>4.5414210107642796E-3</v>
       </c>
-      <c r="E18" s="7"/>
+      <c r="E18" s="8"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
       <c r="C19" s="1">
         <v>7</v>
       </c>
       <c r="D19" s="3">
         <v>6.4272965329950603E-3</v>
       </c>
-      <c r="E19" s="7"/>
+      <c r="E19" s="8"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
       <c r="C20" s="1">
         <v>8</v>
       </c>
       <c r="D20" s="3">
         <v>3.38376634582825E-3</v>
       </c>
-      <c r="E20" s="7"/>
+      <c r="E20" s="8"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
       <c r="C21" s="1">
         <v>9</v>
       </c>
       <c r="D21" s="3">
         <v>7.5523987537550697E-3</v>
       </c>
-      <c r="E21" s="7"/>
+      <c r="E21" s="8"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
       <c r="C22" s="1">
         <v>10</v>
       </c>
       <c r="D22" s="3">
         <v>7.6800340233492996E-3</v>
       </c>
-      <c r="E22" s="7"/>
+      <c r="E22" s="8"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
       <c r="C23" s="1">
         <v>11</v>
       </c>
       <c r="D23" s="3">
         <v>6.3918233917569199E-3</v>
       </c>
-      <c r="E23" s="7"/>
+      <c r="E23" s="8"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7" t="s">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="1">
@@ -1702,118 +1710,118 @@
       <c r="D24" s="3">
         <v>6.8834568210915997E-3</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="9">
         <f>AVERAGE(D24:D33)</f>
         <v>4.7018859667192891E-3</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
       <c r="C25" s="1">
         <v>2</v>
       </c>
       <c r="D25" s="3">
         <v>5.9727451086721804E-3</v>
       </c>
-      <c r="E25" s="7"/>
+      <c r="E25" s="8"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
       <c r="C26" s="1">
         <v>3</v>
       </c>
       <c r="D26" s="3">
         <v>3.2861956035523401E-3</v>
       </c>
-      <c r="E26" s="7"/>
+      <c r="E26" s="8"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
       <c r="C27" s="1">
         <v>4</v>
       </c>
       <c r="D27" s="3">
         <v>4.1621944755989501E-3</v>
       </c>
-      <c r="E27" s="7"/>
+      <c r="E27" s="8"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
       <c r="C28" s="1">
         <v>5</v>
       </c>
       <c r="D28" s="3">
         <v>6.0968354981954303E-3</v>
       </c>
-      <c r="E28" s="7"/>
+      <c r="E28" s="8"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
       <c r="C29" s="1">
         <v>6</v>
       </c>
       <c r="D29" s="3">
         <v>6.8318852941438796E-3</v>
       </c>
-      <c r="E29" s="7"/>
+      <c r="E29" s="8"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
       <c r="C30" s="1">
         <v>7</v>
       </c>
       <c r="D30" s="3">
         <v>3.3675964367588002E-3</v>
       </c>
-      <c r="E30" s="7"/>
+      <c r="E30" s="8"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
       <c r="C31" s="1">
         <v>8</v>
       </c>
       <c r="D31" s="3">
         <v>2.7372032922601602E-3</v>
       </c>
-      <c r="E31" s="7"/>
+      <c r="E31" s="8"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
       <c r="C32" s="1">
         <v>9</v>
       </c>
       <c r="D32" s="3">
         <v>4.0609534836609498E-3</v>
       </c>
-      <c r="E32" s="7"/>
+      <c r="E32" s="8"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
       <c r="C33" s="1">
         <v>10</v>
       </c>
       <c r="D33" s="3">
         <v>3.6197936532585901E-3</v>
       </c>
-      <c r="E33" s="7"/>
+      <c r="E33" s="8"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1860,10 +1868,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -1872,124 +1880,124 @@
       <c r="D2" s="3">
         <v>2.81366470929909E-3</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="9">
         <f>AVERAGE(D2:D12)</f>
         <v>2.8589718670011272E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>2.9086299843656201E-3</v>
       </c>
-      <c r="E3" s="7"/>
+      <c r="E3" s="8"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>2.8725109233065098E-3</v>
       </c>
-      <c r="E4" s="7"/>
+      <c r="E4" s="8"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>2.7472220866062401E-3</v>
       </c>
-      <c r="E5" s="7"/>
+      <c r="E5" s="8"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3">
         <v>2.8395079487722498E-3</v>
       </c>
-      <c r="E6" s="7"/>
+      <c r="E6" s="8"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
       <c r="D7" s="3">
         <v>2.9094927500167801E-3</v>
       </c>
-      <c r="E7" s="7"/>
+      <c r="E7" s="8"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="3">
         <v>2.9300338678111201E-3</v>
       </c>
-      <c r="E8" s="7"/>
+      <c r="E8" s="8"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
       <c r="D9" s="3">
         <v>2.8954508177678399E-3</v>
       </c>
-      <c r="E9" s="7"/>
+      <c r="E9" s="8"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3">
         <v>2.86130290885414E-3</v>
       </c>
-      <c r="E10" s="7"/>
+      <c r="E10" s="8"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
       <c r="D11" s="3">
         <v>2.8834394576333199E-3</v>
       </c>
-      <c r="E11" s="7"/>
+      <c r="E11" s="8"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="3">
         <v>2.7874350825794901E-3</v>
       </c>
-      <c r="E12" s="7"/>
+      <c r="E12" s="8"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7" t="s">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="1">
@@ -1998,124 +2006,124 @@
       <c r="D13" s="3">
         <v>2.4381599990933901E-3</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="9">
         <f>AVERAGE(D13:D23)</f>
         <v>2.6530523100631071E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
       <c r="C14" s="1">
         <v>2</v>
       </c>
       <c r="D14" s="3">
         <v>2.6282434237133502E-3</v>
       </c>
-      <c r="E14" s="7"/>
+      <c r="E14" s="8"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
       <c r="C15" s="1">
         <v>3</v>
       </c>
       <c r="D15" s="3">
         <v>2.3461147455381701E-3</v>
       </c>
-      <c r="E15" s="7"/>
+      <c r="E15" s="8"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
       <c r="C16" s="1">
         <v>4</v>
       </c>
       <c r="D16" s="3">
         <v>2.7524372879068298E-3</v>
       </c>
-      <c r="E16" s="7"/>
+      <c r="E16" s="8"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
       <c r="C17" s="1">
         <v>5</v>
       </c>
       <c r="D17" s="3">
         <v>3.2472745789499402E-3</v>
       </c>
-      <c r="E17" s="7"/>
+      <c r="E17" s="8"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
       <c r="C18" s="1">
         <v>6</v>
       </c>
       <c r="D18" s="3">
         <v>2.5237854282296E-3</v>
       </c>
-      <c r="E18" s="7"/>
+      <c r="E18" s="8"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
       <c r="C19" s="1">
         <v>7</v>
       </c>
       <c r="D19" s="3">
         <v>2.9887873260404599E-3</v>
       </c>
-      <c r="E19" s="7"/>
+      <c r="E19" s="8"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
       <c r="C20" s="1">
         <v>8</v>
       </c>
       <c r="D20" s="3">
         <v>2.06526349558706E-3</v>
       </c>
-      <c r="E20" s="7"/>
+      <c r="E20" s="8"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
       <c r="C21" s="1">
         <v>9</v>
       </c>
       <c r="D21" s="3">
         <v>2.6816447983030599E-3</v>
       </c>
-      <c r="E21" s="7"/>
+      <c r="E21" s="8"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
       <c r="C22" s="1">
         <v>10</v>
       </c>
       <c r="D22" s="3">
         <v>2.7565596821078398E-3</v>
       </c>
-      <c r="E22" s="7"/>
+      <c r="E22" s="8"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
       <c r="C23" s="1">
         <v>11</v>
       </c>
       <c r="D23" s="3">
         <v>2.7553046452244798E-3</v>
       </c>
-      <c r="E23" s="7"/>
+      <c r="E23" s="8"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7" t="s">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="1">
@@ -2124,121 +2132,121 @@
       <c r="D24" s="3">
         <v>3.3099004965032601E-3</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="9">
         <f>AVERAGE(D24:D33)</f>
         <v>2.4948066730810809E-3</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
       <c r="C25" s="1">
         <v>2</v>
       </c>
       <c r="D25" s="3">
         <v>2.0223762558382102E-3</v>
       </c>
-      <c r="E25" s="7"/>
+      <c r="E25" s="8"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
       <c r="C26" s="1">
         <v>3</v>
       </c>
       <c r="D26" s="3">
         <v>2.48460504443907E-3</v>
       </c>
-      <c r="E26" s="7"/>
+      <c r="E26" s="8"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
       <c r="C27" s="1">
         <v>4</v>
       </c>
       <c r="D27" s="3">
         <v>2.1925517311301699E-3</v>
       </c>
-      <c r="E27" s="7"/>
+      <c r="E27" s="8"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
       <c r="C28" s="1">
         <v>5</v>
       </c>
       <c r="D28" s="3">
         <v>2.0210547846704601E-3</v>
       </c>
-      <c r="E28" s="7"/>
+      <c r="E28" s="8"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
       <c r="C29" s="1">
         <v>6</v>
       </c>
       <c r="D29" s="3">
         <v>2.32727791187156E-3</v>
       </c>
-      <c r="E29" s="7"/>
+      <c r="E29" s="8"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
       <c r="C30" s="1">
         <v>7</v>
       </c>
       <c r="D30" s="3">
         <v>3.3527282363668498E-3</v>
       </c>
-      <c r="E30" s="7"/>
+      <c r="E30" s="8"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
       <c r="C31" s="1">
         <v>8</v>
       </c>
       <c r="D31" s="3">
         <v>2.00939520752292E-3</v>
       </c>
-      <c r="E31" s="7"/>
+      <c r="E31" s="8"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
       <c r="C32" s="1">
         <v>9</v>
       </c>
       <c r="D32" s="3">
         <v>2.9226176336739399E-3</v>
       </c>
-      <c r="E32" s="7"/>
+      <c r="E32" s="8"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
       <c r="C33" s="1">
         <v>10</v>
       </c>
       <c r="D33" s="3">
         <v>2.3055594287943698E-3</v>
       </c>
-      <c r="E33" s="7"/>
+      <c r="E33" s="8"/>
       <c r="G33" s="4">
         <v>2.3055594287943698E-3</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/_producao-16-8 copy/_resultados.xlsx
+++ b/_producao-16-8 copy/_resultados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_producao-16-8 copy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD9CB2D-452C-4F2A-BDFD-6A9292123CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD82B91-1E1E-4583-B29A-A81A2807C406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1017,7 +1017,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C042F672-E41D-468F-9A40-AB573A878B0F}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -1289,8 +1289,8 @@
         <v>1.73793482370665E-4</v>
       </c>
       <c r="E24" s="9">
-        <f>AVERAGE(D24:D33)</f>
-        <v>2.0032376576300951E-4</v>
+        <f>AVERAGE(D24:D37)</f>
+        <v>2.1330410891497666E-4</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1392,25 +1392,69 @@
       </c>
       <c r="E33" s="8"/>
     </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="1">
+        <v>11</v>
+      </c>
+      <c r="D34" s="3">
+        <v>3.3565148161274601E-4</v>
+      </c>
+      <c r="E34" s="8"/>
+    </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="1">
+        <v>12</v>
+      </c>
+      <c r="D35" s="6">
+        <v>1.2738871373007399E-4</v>
+      </c>
+      <c r="E35" s="8"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="8"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="1">
+        <v>13</v>
+      </c>
+      <c r="D36" s="3">
+        <v>3.4164426510307702E-4</v>
+      </c>
+      <c r="E36" s="8"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="1">
+        <v>14</v>
+      </c>
+      <c r="D37" s="6">
+        <v>1.78335406733681E-4</v>
+      </c>
+      <c r="E37" s="8"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A2:A33"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A2:A37"/>
     <mergeCell ref="B2:B12"/>
     <mergeCell ref="E2:E12"/>
     <mergeCell ref="B13:B23"/>
     <mergeCell ref="E13:E23"/>
-    <mergeCell ref="B24:B33"/>
-    <mergeCell ref="E24:E33"/>
+    <mergeCell ref="B24:B37"/>
+    <mergeCell ref="E24:E37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/_producao-16-8 copy/_resultados.xlsx
+++ b/_producao-16-8 copy/_resultados.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_producao-16-8 copy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD82B91-1E1E-4583-B29A-A81A2807C406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28445E3-1CD6-4780-929E-6AF0FD6F3D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activity" sheetId="12" r:id="rId1"/>
     <sheet name="Activity (2)" sheetId="16" r:id="rId2"/>
     <sheet name="Age" sheetId="13" r:id="rId3"/>
-    <sheet name="Gender" sheetId="15" r:id="rId4"/>
+    <sheet name="Age (2)" sheetId="17" r:id="rId4"/>
+    <sheet name="Gender" sheetId="15" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="12">
   <si>
     <t>Estratégia</t>
   </si>
@@ -180,7 +181,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -208,6 +209,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -276,7 +283,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -314,6 +321,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1065,7 +1076,7 @@
       <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="16">
         <v>1.5217850441141701E-3</v>
       </c>
       <c r="E3" s="8"/>
@@ -1076,7 +1087,7 @@
       <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="16">
         <v>1.4187702239963399E-3</v>
       </c>
       <c r="E4" s="8"/>
@@ -1105,7 +1116,7 @@
       <c r="C7" s="1">
         <v>6</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="16">
         <v>1.5994412310248701E-3</v>
       </c>
       <c r="E7" s="8"/>
@@ -1116,7 +1127,7 @@
       <c r="C8" s="1">
         <v>7</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="16">
         <v>1.3964272541872899E-3</v>
       </c>
       <c r="E8" s="8"/>
@@ -1127,7 +1138,7 @@
       <c r="C9" s="1">
         <v>8</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="16">
         <v>1.5234914987065399E-3</v>
       </c>
       <c r="E9" s="8"/>
@@ -1147,7 +1158,7 @@
       <c r="C11" s="1">
         <v>10</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="16">
         <v>1.29480134619695E-3</v>
       </c>
       <c r="E11" s="8"/>
@@ -1181,7 +1192,7 @@
       <c r="C14" s="1">
         <v>2</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="16">
         <v>5.46025356640438E-4</v>
       </c>
       <c r="E14" s="14"/>
@@ -1201,7 +1212,7 @@
       <c r="C16" s="1">
         <v>4</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="16">
         <v>4.5331415788522699E-4</v>
       </c>
       <c r="E16" s="14"/>
@@ -1230,7 +1241,7 @@
       <c r="C19" s="1">
         <v>7</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="16">
         <v>5.4759582523591596E-4</v>
       </c>
       <c r="E19" s="14"/>
@@ -1250,7 +1261,7 @@
       <c r="C21" s="1">
         <v>9</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="16">
         <v>8.9001901515576199E-4</v>
       </c>
       <c r="E21" s="14"/>
@@ -1261,7 +1272,7 @@
       <c r="C22" s="1">
         <v>10</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="16">
         <v>8.6876944325313898E-4</v>
       </c>
       <c r="E22" s="14"/>
@@ -1272,7 +1283,7 @@
       <c r="C23" s="1">
         <v>11</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="16">
         <v>5.9022203911008697E-4</v>
       </c>
       <c r="E23" s="15"/>
@@ -1482,7 +1493,7 @@
       <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="17" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -1884,6 +1895,408 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88B8560C-6760-4F2C-BEB3-D4C8A79DCAAF}">
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.77734375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="22.77734375" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="9">
+        <f>AVERAGE(D2:D12)</f>
+        <v>7.5204771451239999E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="16">
+        <v>7.7222014481316001E-3</v>
+      </c>
+      <c r="E3" s="8"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="16">
+        <v>7.4276032951078701E-3</v>
+      </c>
+      <c r="E4" s="8"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="8"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="1">
+        <v>6</v>
+      </c>
+      <c r="D7" s="16">
+        <v>7.9683523176790998E-3</v>
+      </c>
+      <c r="E7" s="8"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="1">
+        <v>7</v>
+      </c>
+      <c r="D8" s="16">
+        <v>7.1325304703669396E-3</v>
+      </c>
+      <c r="E8" s="8"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="1">
+        <v>8</v>
+      </c>
+      <c r="D9" s="16">
+        <v>7.6723666731501597E-3</v>
+      </c>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="1">
+        <v>9</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="8"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="1">
+        <v>10</v>
+      </c>
+      <c r="D11" s="16">
+        <v>7.1998086663083299E-3</v>
+      </c>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="1">
+        <v>11</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="8"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="9">
+        <f>AVERAGE(D13:D23)</f>
+        <v>6.5940540634390936E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="1">
+        <v>2</v>
+      </c>
+      <c r="D14" s="16">
+        <v>6.0285373262784596E-3</v>
+      </c>
+      <c r="E14" s="8"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="1">
+        <v>3</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="8"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="1">
+        <v>4</v>
+      </c>
+      <c r="D16" s="16">
+        <v>5.4842343524997596E-3</v>
+      </c>
+      <c r="E16" s="8"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="1">
+        <v>5</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="8"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="1">
+        <v>6</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="8"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="1">
+        <v>7</v>
+      </c>
+      <c r="D19" s="16">
+        <v>6.4272965329950603E-3</v>
+      </c>
+      <c r="E19" s="8"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="1">
+        <v>8</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="8"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="1">
+        <v>9</v>
+      </c>
+      <c r="D21" s="16">
+        <v>7.5523987537550697E-3</v>
+      </c>
+      <c r="E21" s="8"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="1">
+        <v>10</v>
+      </c>
+      <c r="D22" s="16">
+        <v>7.6800340233492996E-3</v>
+      </c>
+      <c r="E22" s="8"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="1">
+        <v>11</v>
+      </c>
+      <c r="D23" s="16">
+        <v>6.3918233917569199E-3</v>
+      </c>
+      <c r="E23" s="8"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3">
+        <v>6.8834568210915997E-3</v>
+      </c>
+      <c r="E24" s="9">
+        <f>AVERAGE(D24:D33)</f>
+        <v>4.7018859667192891E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="1">
+        <v>2</v>
+      </c>
+      <c r="D25" s="3">
+        <v>5.9727451086721804E-3</v>
+      </c>
+      <c r="E25" s="8"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="1">
+        <v>3</v>
+      </c>
+      <c r="D26" s="6">
+        <v>3.2861956035523401E-3</v>
+      </c>
+      <c r="E26" s="8"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="1">
+        <v>4</v>
+      </c>
+      <c r="D27" s="6">
+        <v>4.1621944755989501E-3</v>
+      </c>
+      <c r="E27" s="8"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="1">
+        <v>5</v>
+      </c>
+      <c r="D28" s="3">
+        <v>6.0968354981954303E-3</v>
+      </c>
+      <c r="E28" s="8"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="1">
+        <v>6</v>
+      </c>
+      <c r="D29" s="3">
+        <v>6.8318852941438796E-3</v>
+      </c>
+      <c r="E29" s="8"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="1">
+        <v>7</v>
+      </c>
+      <c r="D30" s="6">
+        <v>3.3675964367588002E-3</v>
+      </c>
+      <c r="E30" s="8"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="1">
+        <v>8</v>
+      </c>
+      <c r="D31" s="6">
+        <v>2.7372032922601602E-3</v>
+      </c>
+      <c r="E31" s="8"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="1">
+        <v>9</v>
+      </c>
+      <c r="D32" s="6">
+        <v>4.0609534836609498E-3</v>
+      </c>
+      <c r="E32" s="8"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="1">
+        <v>10</v>
+      </c>
+      <c r="D33" s="6">
+        <v>3.6197936532585901E-3</v>
+      </c>
+      <c r="E33" s="8"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A2:A33"/>
+    <mergeCell ref="B2:B12"/>
+    <mergeCell ref="E2:E12"/>
+    <mergeCell ref="B13:B23"/>
+    <mergeCell ref="E13:E23"/>
+    <mergeCell ref="B24:B33"/>
+    <mergeCell ref="E24:E33"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0018FF42-DB9B-49FF-AD34-CF6CC8AED773}">
   <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/_producao-16-8 copy/_resultados.xlsx
+++ b/_producao-16-8 copy/_resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_producao-16-8 copy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28445E3-1CD6-4780-929E-6AF0FD6F3D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E18017-8258-4F49-AD45-049096C1EBB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activity" sheetId="12" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Age" sheetId="13" r:id="rId3"/>
     <sheet name="Age (2)" sheetId="17" r:id="rId4"/>
     <sheet name="Gender" sheetId="15" r:id="rId5"/>
+    <sheet name="Gender (2)" sheetId="18" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="12">
   <si>
     <t>Estratégia</t>
   </si>
@@ -295,6 +296,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -321,10 +326,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -633,10 +634,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -645,124 +646,124 @@
       <c r="D2" s="3">
         <v>1.22740707443255E-3</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="11">
         <f>AVERAGE(D2:D12)</f>
         <v>1.3405988398128117E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>1.5217850441141701E-3</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="E3" s="10"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>1.4187702239963399E-3</v>
       </c>
-      <c r="E4" s="8"/>
+      <c r="E4" s="10"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>1.21923057588587E-3</v>
       </c>
-      <c r="E5" s="8"/>
+      <c r="E5" s="10"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3">
         <v>1.2107251197056299E-3</v>
       </c>
-      <c r="E6" s="8"/>
+      <c r="E6" s="10"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
       <c r="D7" s="3">
         <v>1.5994412310248701E-3</v>
       </c>
-      <c r="E7" s="8"/>
+      <c r="E7" s="10"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="3">
         <v>1.3964272541872899E-3</v>
       </c>
-      <c r="E8" s="8"/>
+      <c r="E8" s="10"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
       <c r="D9" s="3">
         <v>1.5234914987065399E-3</v>
       </c>
-      <c r="E9" s="8"/>
+      <c r="E9" s="10"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3">
         <v>1.14432918115938E-3</v>
       </c>
-      <c r="E10" s="8"/>
+      <c r="E10" s="10"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
       <c r="D11" s="3">
         <v>1.29480134619695E-3</v>
       </c>
-      <c r="E11" s="8"/>
+      <c r="E11" s="10"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="3">
         <v>1.1901786885313401E-3</v>
       </c>
-      <c r="E12" s="8"/>
+      <c r="E12" s="10"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="10" t="s">
+      <c r="A13" s="10"/>
+      <c r="B13" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="1">
@@ -771,124 +772,124 @@
       <c r="D13" s="3">
         <v>1.76494351019696E-4</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="15">
         <f>AVERAGE(D13:D23)</f>
         <v>4.6044642516324585E-4</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="11"/>
+      <c r="A14" s="10"/>
+      <c r="B14" s="13"/>
       <c r="C14" s="1">
         <v>2</v>
       </c>
       <c r="D14" s="3">
         <v>5.46025356640438E-4</v>
       </c>
-      <c r="E14" s="14"/>
+      <c r="E14" s="16"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="11"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="13"/>
       <c r="C15" s="1">
         <v>3</v>
       </c>
       <c r="D15" s="3">
         <v>1.7489087688418899E-4</v>
       </c>
-      <c r="E15" s="14"/>
+      <c r="E15" s="16"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="11"/>
+      <c r="A16" s="10"/>
+      <c r="B16" s="13"/>
       <c r="C16" s="1">
         <v>4</v>
       </c>
       <c r="D16" s="3">
         <v>4.5331415788522699E-4</v>
       </c>
-      <c r="E16" s="14"/>
+      <c r="E16" s="16"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="11"/>
+      <c r="A17" s="10"/>
+      <c r="B17" s="13"/>
       <c r="C17" s="1">
         <v>5</v>
       </c>
       <c r="D17" s="3">
         <v>4.5224030226177498E-4</v>
       </c>
-      <c r="E17" s="14"/>
+      <c r="E17" s="16"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="11"/>
+      <c r="A18" s="10"/>
+      <c r="B18" s="13"/>
       <c r="C18" s="1">
         <v>6</v>
       </c>
       <c r="D18" s="3">
         <v>3.25042909349475E-4</v>
       </c>
-      <c r="E18" s="14"/>
+      <c r="E18" s="16"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="11"/>
+      <c r="A19" s="10"/>
+      <c r="B19" s="13"/>
       <c r="C19" s="1">
         <v>7</v>
       </c>
       <c r="D19" s="3">
         <v>5.4759582523591596E-4</v>
       </c>
-      <c r="E19" s="14"/>
+      <c r="E19" s="16"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="11"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="13"/>
       <c r="C20" s="1">
         <v>8</v>
       </c>
       <c r="D20" s="3">
         <v>4.0296400000000003E-5</v>
       </c>
-      <c r="E20" s="14"/>
+      <c r="E20" s="16"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="11"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="13"/>
       <c r="C21" s="1">
         <v>9</v>
       </c>
       <c r="D21" s="3">
         <v>8.9001901515576199E-4</v>
       </c>
-      <c r="E21" s="14"/>
+      <c r="E21" s="16"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="11"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="13"/>
       <c r="C22" s="1">
         <v>10</v>
       </c>
       <c r="D22" s="3">
         <v>8.6876944325313898E-4</v>
       </c>
-      <c r="E22" s="14"/>
+      <c r="E22" s="16"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="12"/>
+      <c r="A23" s="10"/>
+      <c r="B23" s="14"/>
       <c r="C23" s="1">
         <v>11</v>
       </c>
       <c r="D23" s="3">
         <v>5.9022203911008697E-4</v>
       </c>
-      <c r="E23" s="15"/>
+      <c r="E23" s="17"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8" t="s">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="1">
@@ -897,118 +898,118 @@
       <c r="D24" s="3">
         <v>1.73793482370665E-4</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="11">
         <f>AVERAGE(D24:D33)</f>
         <v>2.0032376576300951E-4</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
       <c r="C25" s="1">
         <v>2</v>
       </c>
       <c r="D25" s="3">
         <v>4.4079599999999997E-5</v>
       </c>
-      <c r="E25" s="8"/>
+      <c r="E25" s="10"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
       <c r="C26" s="1">
         <v>3</v>
       </c>
       <c r="D26" s="3">
         <v>1.9820721733818201E-4</v>
       </c>
-      <c r="E26" s="8"/>
+      <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
       <c r="C27" s="1">
         <v>4</v>
       </c>
       <c r="D27" s="3">
         <v>2.6898882604876098E-4</v>
       </c>
-      <c r="E27" s="8"/>
+      <c r="E27" s="10"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
       <c r="C28" s="1">
         <v>5</v>
       </c>
       <c r="D28" s="3">
         <v>9.9348000000000002E-6</v>
       </c>
-      <c r="E28" s="8"/>
+      <c r="E28" s="10"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
       <c r="C29" s="1">
         <v>6</v>
       </c>
       <c r="D29" s="3">
         <v>1.70899292234211E-4</v>
       </c>
-      <c r="E29" s="8"/>
+      <c r="E29" s="10"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
       <c r="C30" s="1">
         <v>7</v>
       </c>
       <c r="D30" s="3">
         <v>3.7644454634369102E-4</v>
       </c>
-      <c r="E30" s="8"/>
+      <c r="E30" s="10"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
       <c r="C31" s="1">
         <v>8</v>
       </c>
       <c r="D31" s="3">
         <v>7.5758852866904895E-5</v>
       </c>
-      <c r="E31" s="8"/>
+      <c r="E31" s="10"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
       <c r="C32" s="1">
         <v>9</v>
       </c>
       <c r="D32" s="3">
         <v>4.9271851899704603E-4</v>
       </c>
-      <c r="E32" s="8"/>
+      <c r="E32" s="10"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
       <c r="C33" s="1">
         <v>10</v>
       </c>
       <c r="D33" s="3">
         <v>1.9241252143063401E-4</v>
       </c>
-      <c r="E33" s="8"/>
+      <c r="E33" s="10"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1055,242 +1056,242 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="9">
+      <c r="E2" s="11">
         <f>AVERAGE(D2:D12)</f>
         <v>1.4591194330376932E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="7">
         <v>1.5217850441141701E-3</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="E3" s="10"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="7">
         <v>1.4187702239963399E-3</v>
       </c>
-      <c r="E4" s="8"/>
+      <c r="E4" s="10"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="8"/>
+      <c r="E5" s="10"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="8"/>
+      <c r="E6" s="10"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="7">
         <v>1.5994412310248701E-3</v>
       </c>
-      <c r="E7" s="8"/>
+      <c r="E7" s="10"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="7">
         <v>1.3964272541872899E-3</v>
       </c>
-      <c r="E8" s="8"/>
+      <c r="E8" s="10"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="7">
         <v>1.5234914987065399E-3</v>
       </c>
-      <c r="E9" s="8"/>
+      <c r="E9" s="10"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="8"/>
+      <c r="E10" s="10"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="7">
         <v>1.29480134619695E-3</v>
       </c>
-      <c r="E11" s="8"/>
+      <c r="E11" s="10"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="3"/>
-      <c r="E12" s="8"/>
+      <c r="E12" s="10"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="10" t="s">
+      <c r="A13" s="10"/>
+      <c r="B13" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="1">
         <v>1</v>
       </c>
       <c r="D13" s="3"/>
-      <c r="E13" s="13">
+      <c r="E13" s="15">
         <f>AVERAGE(D13:D23)</f>
         <v>6.4932430621342815E-4</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="11"/>
+      <c r="A14" s="10"/>
+      <c r="B14" s="13"/>
       <c r="C14" s="1">
         <v>2</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="7">
         <v>5.46025356640438E-4</v>
       </c>
-      <c r="E14" s="14"/>
+      <c r="E14" s="16"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="11"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="13"/>
       <c r="C15" s="1">
         <v>3</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="14"/>
+      <c r="E15" s="16"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="11"/>
+      <c r="A16" s="10"/>
+      <c r="B16" s="13"/>
       <c r="C16" s="1">
         <v>4</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="7">
         <v>4.5331415788522699E-4</v>
       </c>
-      <c r="E16" s="14"/>
+      <c r="E16" s="16"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="11"/>
+      <c r="A17" s="10"/>
+      <c r="B17" s="13"/>
       <c r="C17" s="1">
         <v>5</v>
       </c>
       <c r="D17" s="3"/>
-      <c r="E17" s="14"/>
+      <c r="E17" s="16"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="11"/>
+      <c r="A18" s="10"/>
+      <c r="B18" s="13"/>
       <c r="C18" s="1">
         <v>6</v>
       </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="14"/>
+      <c r="E18" s="16"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="11"/>
+      <c r="A19" s="10"/>
+      <c r="B19" s="13"/>
       <c r="C19" s="1">
         <v>7</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="7">
         <v>5.4759582523591596E-4</v>
       </c>
-      <c r="E19" s="14"/>
+      <c r="E19" s="16"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="11"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="13"/>
       <c r="C20" s="1">
         <v>8</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="14"/>
+      <c r="E20" s="16"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="11"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="13"/>
       <c r="C21" s="1">
         <v>9</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="7">
         <v>8.9001901515576199E-4</v>
       </c>
-      <c r="E21" s="14"/>
+      <c r="E21" s="16"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="11"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="13"/>
       <c r="C22" s="1">
         <v>10</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="7">
         <v>8.6876944325313898E-4</v>
       </c>
-      <c r="E22" s="14"/>
+      <c r="E22" s="16"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="12"/>
+      <c r="A23" s="10"/>
+      <c r="B23" s="14"/>
       <c r="C23" s="1">
         <v>11</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="7">
         <v>5.9022203911008697E-4</v>
       </c>
-      <c r="E23" s="15"/>
+      <c r="E23" s="17"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8" t="s">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="1">
@@ -1299,162 +1300,162 @@
       <c r="D24" s="6">
         <v>1.73793482370665E-4</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="11">
         <f>AVERAGE(D24:D37)</f>
         <v>2.1330410891497666E-4</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
       <c r="C25" s="1">
         <v>2</v>
       </c>
       <c r="D25" s="3">
         <v>4.4079599999999997E-5</v>
       </c>
-      <c r="E25" s="8"/>
+      <c r="E25" s="10"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
       <c r="C26" s="1">
         <v>3</v>
       </c>
       <c r="D26" s="6">
         <v>1.9820721733818201E-4</v>
       </c>
-      <c r="E26" s="8"/>
+      <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
       <c r="C27" s="1">
         <v>4</v>
       </c>
       <c r="D27" s="3">
         <v>2.6898882604876098E-4</v>
       </c>
-      <c r="E27" s="8"/>
+      <c r="E27" s="10"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
       <c r="C28" s="1">
         <v>5</v>
       </c>
       <c r="D28" s="3">
         <v>9.9348000000000002E-6</v>
       </c>
-      <c r="E28" s="8"/>
+      <c r="E28" s="10"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
       <c r="C29" s="1">
         <v>6</v>
       </c>
       <c r="D29" s="6">
         <v>1.70899292234211E-4</v>
       </c>
-      <c r="E29" s="8"/>
+      <c r="E29" s="10"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
       <c r="C30" s="1">
         <v>7</v>
       </c>
       <c r="D30" s="3">
         <v>3.7644454634369102E-4</v>
       </c>
-      <c r="E30" s="8"/>
+      <c r="E30" s="10"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
       <c r="C31" s="1">
         <v>8</v>
       </c>
       <c r="D31" s="3">
         <v>7.5758852866904895E-5</v>
       </c>
-      <c r="E31" s="8"/>
+      <c r="E31" s="10"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
       <c r="C32" s="1">
         <v>9</v>
       </c>
       <c r="D32" s="3">
         <v>4.9271851899704603E-4</v>
       </c>
-      <c r="E32" s="8"/>
+      <c r="E32" s="10"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
       <c r="C33" s="1">
         <v>10</v>
       </c>
       <c r="D33" s="6">
         <v>1.9241252143063401E-4</v>
       </c>
-      <c r="E33" s="8"/>
+      <c r="E33" s="10"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
       <c r="C34" s="1">
         <v>11</v>
       </c>
       <c r="D34" s="3">
         <v>3.3565148161274601E-4</v>
       </c>
-      <c r="E34" s="8"/>
+      <c r="E34" s="10"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
       <c r="C35" s="1">
         <v>12</v>
       </c>
       <c r="D35" s="6">
         <v>1.2738871373007399E-4</v>
       </c>
-      <c r="E35" s="8"/>
+      <c r="E35" s="10"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
+      <c r="A36" s="10"/>
+      <c r="B36" s="10"/>
       <c r="C36" s="1">
         <v>13</v>
       </c>
       <c r="D36" s="3">
         <v>3.4164426510307702E-4</v>
       </c>
-      <c r="E36" s="8"/>
+      <c r="E36" s="10"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
+      <c r="A37" s="10"/>
+      <c r="B37" s="10"/>
       <c r="C37" s="1">
         <v>14</v>
       </c>
       <c r="D37" s="6">
         <v>1.78335406733681E-4</v>
       </c>
-      <c r="E37" s="8"/>
+      <c r="E37" s="10"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1493,7 +1494,7 @@
       <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="8" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -1501,10 +1502,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -1513,124 +1514,124 @@
       <c r="D2" s="3">
         <v>6.8494550335423199E-3</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="11">
         <f>AVERAGE(D2:D12)</f>
         <v>7.2093580443383567E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>7.7222014481316001E-3</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="E3" s="10"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>7.4276032951078701E-3</v>
       </c>
-      <c r="E4" s="8"/>
+      <c r="E4" s="10"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>6.9163642363323698E-3</v>
       </c>
-      <c r="E5" s="8"/>
+      <c r="E5" s="10"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3">
         <v>7.1247468487415202E-3</v>
       </c>
-      <c r="E6" s="8"/>
+      <c r="E6" s="10"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
       <c r="D7" s="3">
         <v>7.9683523176790998E-3</v>
       </c>
-      <c r="E7" s="8"/>
+      <c r="E7" s="10"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="3">
         <v>7.1325304703669396E-3</v>
       </c>
-      <c r="E8" s="8"/>
+      <c r="E8" s="10"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
       <c r="D9" s="3">
         <v>7.6723666731501597E-3</v>
       </c>
-      <c r="E9" s="8"/>
+      <c r="E9" s="10"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3">
         <v>6.44864466466859E-3</v>
       </c>
-      <c r="E10" s="8"/>
+      <c r="E10" s="10"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
       <c r="D11" s="3">
         <v>7.1998086663083299E-3</v>
       </c>
-      <c r="E11" s="8"/>
+      <c r="E11" s="10"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="3">
         <v>6.8408648336931201E-3</v>
       </c>
-      <c r="E12" s="8"/>
+      <c r="E12" s="10"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8" t="s">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="1">
@@ -1639,124 +1640,124 @@
       <c r="D13" s="3">
         <v>4.4059430113216501E-3</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="11">
         <f>AVERAGE(D13:D23)</f>
         <v>5.6171193080640424E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
       <c r="C14" s="1">
         <v>2</v>
       </c>
       <c r="D14" s="3">
         <v>6.0285373262784596E-3</v>
       </c>
-      <c r="E14" s="8"/>
+      <c r="E14" s="10"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
       <c r="C15" s="1">
         <v>3</v>
       </c>
       <c r="D15" s="3">
         <v>4.6542086132795998E-3</v>
       </c>
-      <c r="E15" s="8"/>
+      <c r="E15" s="10"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
       <c r="C16" s="1">
         <v>4</v>
       </c>
       <c r="D16" s="3">
         <v>5.4842343524997596E-3</v>
       </c>
-      <c r="E16" s="8"/>
+      <c r="E16" s="10"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
       <c r="C17" s="1">
         <v>5</v>
       </c>
       <c r="D17" s="3">
         <v>5.2386490268761304E-3</v>
       </c>
-      <c r="E17" s="8"/>
+      <c r="E17" s="10"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
       <c r="C18" s="1">
         <v>6</v>
       </c>
       <c r="D18" s="3">
         <v>4.5414210107642796E-3</v>
       </c>
-      <c r="E18" s="8"/>
+      <c r="E18" s="10"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
       <c r="C19" s="1">
         <v>7</v>
       </c>
       <c r="D19" s="3">
         <v>6.4272965329950603E-3</v>
       </c>
-      <c r="E19" s="8"/>
+      <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
       <c r="C20" s="1">
         <v>8</v>
       </c>
       <c r="D20" s="3">
         <v>3.38376634582825E-3</v>
       </c>
-      <c r="E20" s="8"/>
+      <c r="E20" s="10"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
       <c r="C21" s="1">
         <v>9</v>
       </c>
       <c r="D21" s="3">
         <v>7.5523987537550697E-3</v>
       </c>
-      <c r="E21" s="8"/>
+      <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
       <c r="C22" s="1">
         <v>10</v>
       </c>
       <c r="D22" s="3">
         <v>7.6800340233492996E-3</v>
       </c>
-      <c r="E22" s="8"/>
+      <c r="E22" s="10"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
       <c r="C23" s="1">
         <v>11</v>
       </c>
       <c r="D23" s="3">
         <v>6.3918233917569199E-3</v>
       </c>
-      <c r="E23" s="8"/>
+      <c r="E23" s="10"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8" t="s">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="1">
@@ -1765,118 +1766,118 @@
       <c r="D24" s="3">
         <v>6.8834568210915997E-3</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="11">
         <f>AVERAGE(D24:D33)</f>
         <v>4.7018859667192891E-3</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
       <c r="C25" s="1">
         <v>2</v>
       </c>
       <c r="D25" s="3">
         <v>5.9727451086721804E-3</v>
       </c>
-      <c r="E25" s="8"/>
+      <c r="E25" s="10"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
       <c r="C26" s="1">
         <v>3</v>
       </c>
       <c r="D26" s="3">
         <v>3.2861956035523401E-3</v>
       </c>
-      <c r="E26" s="8"/>
+      <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
       <c r="C27" s="1">
         <v>4</v>
       </c>
       <c r="D27" s="3">
         <v>4.1621944755989501E-3</v>
       </c>
-      <c r="E27" s="8"/>
+      <c r="E27" s="10"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
       <c r="C28" s="1">
         <v>5</v>
       </c>
       <c r="D28" s="3">
         <v>6.0968354981954303E-3</v>
       </c>
-      <c r="E28" s="8"/>
+      <c r="E28" s="10"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
       <c r="C29" s="1">
         <v>6</v>
       </c>
       <c r="D29" s="3">
         <v>6.8318852941438796E-3</v>
       </c>
-      <c r="E29" s="8"/>
+      <c r="E29" s="10"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
       <c r="C30" s="1">
         <v>7</v>
       </c>
       <c r="D30" s="3">
         <v>3.3675964367588002E-3</v>
       </c>
-      <c r="E30" s="8"/>
+      <c r="E30" s="10"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
       <c r="C31" s="1">
         <v>8</v>
       </c>
       <c r="D31" s="3">
         <v>2.7372032922601602E-3</v>
       </c>
-      <c r="E31" s="8"/>
+      <c r="E31" s="10"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
       <c r="C32" s="1">
         <v>9</v>
       </c>
       <c r="D32" s="3">
         <v>4.0609534836609498E-3</v>
       </c>
-      <c r="E32" s="8"/>
+      <c r="E32" s="10"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
       <c r="C33" s="1">
         <v>10</v>
       </c>
       <c r="D33" s="3">
         <v>3.6197936532585901E-3</v>
       </c>
-      <c r="E33" s="8"/>
+      <c r="E33" s="10"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1923,242 +1924,242 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="9">
+      <c r="E2" s="11">
         <f>AVERAGE(D2:D12)</f>
         <v>7.5204771451239999E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="7">
         <v>7.7222014481316001E-3</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="E3" s="10"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="7">
         <v>7.4276032951078701E-3</v>
       </c>
-      <c r="E4" s="8"/>
+      <c r="E4" s="10"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="8"/>
+      <c r="E5" s="10"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="8"/>
+      <c r="E6" s="10"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="7">
         <v>7.9683523176790998E-3</v>
       </c>
-      <c r="E7" s="8"/>
+      <c r="E7" s="10"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="7">
         <v>7.1325304703669396E-3</v>
       </c>
-      <c r="E8" s="8"/>
+      <c r="E8" s="10"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="7">
         <v>7.6723666731501597E-3</v>
       </c>
-      <c r="E9" s="8"/>
+      <c r="E9" s="10"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="8"/>
+      <c r="E10" s="10"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="7">
         <v>7.1998086663083299E-3</v>
       </c>
-      <c r="E11" s="8"/>
+      <c r="E11" s="10"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="3"/>
-      <c r="E12" s="8"/>
+      <c r="E12" s="10"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8" t="s">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="1">
         <v>1</v>
       </c>
       <c r="D13" s="3"/>
-      <c r="E13" s="9">
+      <c r="E13" s="11">
         <f>AVERAGE(D13:D23)</f>
         <v>6.5940540634390936E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
       <c r="C14" s="1">
         <v>2</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="7">
         <v>6.0285373262784596E-3</v>
       </c>
-      <c r="E14" s="8"/>
+      <c r="E14" s="10"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
       <c r="C15" s="1">
         <v>3</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="8"/>
+      <c r="E15" s="10"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
       <c r="C16" s="1">
         <v>4</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="7">
         <v>5.4842343524997596E-3</v>
       </c>
-      <c r="E16" s="8"/>
+      <c r="E16" s="10"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
       <c r="C17" s="1">
         <v>5</v>
       </c>
       <c r="D17" s="3"/>
-      <c r="E17" s="8"/>
+      <c r="E17" s="10"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
       <c r="C18" s="1">
         <v>6</v>
       </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="8"/>
+      <c r="E18" s="10"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
       <c r="C19" s="1">
         <v>7</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="7">
         <v>6.4272965329950603E-3</v>
       </c>
-      <c r="E19" s="8"/>
+      <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
       <c r="C20" s="1">
         <v>8</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="8"/>
+      <c r="E20" s="10"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
       <c r="C21" s="1">
         <v>9</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="7">
         <v>7.5523987537550697E-3</v>
       </c>
-      <c r="E21" s="8"/>
+      <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
       <c r="C22" s="1">
         <v>10</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="7">
         <v>7.6800340233492996E-3</v>
       </c>
-      <c r="E22" s="8"/>
+      <c r="E22" s="10"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
       <c r="C23" s="1">
         <v>11</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="7">
         <v>6.3918233917569199E-3</v>
       </c>
-      <c r="E23" s="8"/>
+      <c r="E23" s="10"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8" t="s">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="1">
@@ -2167,118 +2168,118 @@
       <c r="D24" s="3">
         <v>6.8834568210915997E-3</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="11">
         <f>AVERAGE(D24:D33)</f>
         <v>4.7018859667192891E-3</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
       <c r="C25" s="1">
         <v>2</v>
       </c>
       <c r="D25" s="3">
         <v>5.9727451086721804E-3</v>
       </c>
-      <c r="E25" s="8"/>
+      <c r="E25" s="10"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
       <c r="C26" s="1">
         <v>3</v>
       </c>
       <c r="D26" s="6">
         <v>3.2861956035523401E-3</v>
       </c>
-      <c r="E26" s="8"/>
+      <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
       <c r="C27" s="1">
         <v>4</v>
       </c>
       <c r="D27" s="6">
         <v>4.1621944755989501E-3</v>
       </c>
-      <c r="E27" s="8"/>
+      <c r="E27" s="10"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
       <c r="C28" s="1">
         <v>5</v>
       </c>
       <c r="D28" s="3">
         <v>6.0968354981954303E-3</v>
       </c>
-      <c r="E28" s="8"/>
+      <c r="E28" s="10"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
       <c r="C29" s="1">
         <v>6</v>
       </c>
       <c r="D29" s="3">
         <v>6.8318852941438796E-3</v>
       </c>
-      <c r="E29" s="8"/>
+      <c r="E29" s="10"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
       <c r="C30" s="1">
         <v>7</v>
       </c>
       <c r="D30" s="6">
         <v>3.3675964367588002E-3</v>
       </c>
-      <c r="E30" s="8"/>
+      <c r="E30" s="10"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
       <c r="C31" s="1">
         <v>8</v>
       </c>
       <c r="D31" s="6">
         <v>2.7372032922601602E-3</v>
       </c>
-      <c r="E31" s="8"/>
+      <c r="E31" s="10"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
       <c r="C32" s="1">
         <v>9</v>
       </c>
       <c r="D32" s="6">
         <v>4.0609534836609498E-3</v>
       </c>
-      <c r="E32" s="8"/>
+      <c r="E32" s="10"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
       <c r="C33" s="1">
         <v>10</v>
       </c>
       <c r="D33" s="6">
         <v>3.6197936532585901E-3</v>
       </c>
-      <c r="E33" s="8"/>
+      <c r="E33" s="10"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2325,10 +2326,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -2337,124 +2338,124 @@
       <c r="D2" s="3">
         <v>2.81366470929909E-3</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="11">
         <f>AVERAGE(D2:D12)</f>
         <v>2.8589718670011272E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>2.9086299843656201E-3</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="E3" s="10"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>2.8725109233065098E-3</v>
       </c>
-      <c r="E4" s="8"/>
+      <c r="E4" s="10"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>2.7472220866062401E-3</v>
       </c>
-      <c r="E5" s="8"/>
+      <c r="E5" s="10"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3">
         <v>2.8395079487722498E-3</v>
       </c>
-      <c r="E6" s="8"/>
+      <c r="E6" s="10"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
       <c r="D7" s="3">
         <v>2.9094927500167801E-3</v>
       </c>
-      <c r="E7" s="8"/>
+      <c r="E7" s="10"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="3">
         <v>2.9300338678111201E-3</v>
       </c>
-      <c r="E8" s="8"/>
+      <c r="E8" s="10"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
       <c r="D9" s="3">
         <v>2.8954508177678399E-3</v>
       </c>
-      <c r="E9" s="8"/>
+      <c r="E9" s="10"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3">
         <v>2.86130290885414E-3</v>
       </c>
-      <c r="E10" s="8"/>
+      <c r="E10" s="10"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
       <c r="D11" s="3">
         <v>2.8834394576333199E-3</v>
       </c>
-      <c r="E11" s="8"/>
+      <c r="E11" s="10"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="3">
         <v>2.7874350825794901E-3</v>
       </c>
-      <c r="E12" s="8"/>
+      <c r="E12" s="10"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8" t="s">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="1">
@@ -2463,124 +2464,124 @@
       <c r="D13" s="3">
         <v>2.4381599990933901E-3</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="11">
         <f>AVERAGE(D13:D23)</f>
         <v>2.6530523100631071E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
       <c r="C14" s="1">
         <v>2</v>
       </c>
       <c r="D14" s="3">
         <v>2.6282434237133502E-3</v>
       </c>
-      <c r="E14" s="8"/>
+      <c r="E14" s="10"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
       <c r="C15" s="1">
         <v>3</v>
       </c>
       <c r="D15" s="3">
         <v>2.3461147455381701E-3</v>
       </c>
-      <c r="E15" s="8"/>
+      <c r="E15" s="10"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
       <c r="C16" s="1">
         <v>4</v>
       </c>
       <c r="D16" s="3">
         <v>2.7524372879068298E-3</v>
       </c>
-      <c r="E16" s="8"/>
+      <c r="E16" s="10"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
       <c r="C17" s="1">
         <v>5</v>
       </c>
       <c r="D17" s="3">
         <v>3.2472745789499402E-3</v>
       </c>
-      <c r="E17" s="8"/>
+      <c r="E17" s="10"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
       <c r="C18" s="1">
         <v>6</v>
       </c>
       <c r="D18" s="3">
         <v>2.5237854282296E-3</v>
       </c>
-      <c r="E18" s="8"/>
+      <c r="E18" s="10"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
       <c r="C19" s="1">
         <v>7</v>
       </c>
       <c r="D19" s="3">
         <v>2.9887873260404599E-3</v>
       </c>
-      <c r="E19" s="8"/>
+      <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
       <c r="C20" s="1">
         <v>8</v>
       </c>
       <c r="D20" s="3">
         <v>2.06526349558706E-3</v>
       </c>
-      <c r="E20" s="8"/>
+      <c r="E20" s="10"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
       <c r="C21" s="1">
         <v>9</v>
       </c>
       <c r="D21" s="3">
         <v>2.6816447983030599E-3</v>
       </c>
-      <c r="E21" s="8"/>
+      <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
       <c r="C22" s="1">
         <v>10</v>
       </c>
       <c r="D22" s="3">
         <v>2.7565596821078398E-3</v>
       </c>
-      <c r="E22" s="8"/>
+      <c r="E22" s="10"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
       <c r="C23" s="1">
         <v>11</v>
       </c>
       <c r="D23" s="3">
         <v>2.7553046452244798E-3</v>
       </c>
-      <c r="E23" s="8"/>
+      <c r="E23" s="10"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8" t="s">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="1">
@@ -2589,121 +2590,515 @@
       <c r="D24" s="3">
         <v>3.3099004965032601E-3</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="11">
         <f>AVERAGE(D24:D33)</f>
         <v>2.4948066730810809E-3</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
       <c r="C25" s="1">
         <v>2</v>
       </c>
       <c r="D25" s="3">
         <v>2.0223762558382102E-3</v>
       </c>
-      <c r="E25" s="8"/>
+      <c r="E25" s="10"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
       <c r="C26" s="1">
         <v>3</v>
       </c>
       <c r="D26" s="3">
         <v>2.48460504443907E-3</v>
       </c>
-      <c r="E26" s="8"/>
+      <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
       <c r="C27" s="1">
         <v>4</v>
       </c>
       <c r="D27" s="3">
         <v>2.1925517311301699E-3</v>
       </c>
-      <c r="E27" s="8"/>
+      <c r="E27" s="10"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
       <c r="C28" s="1">
         <v>5</v>
       </c>
       <c r="D28" s="3">
         <v>2.0210547846704601E-3</v>
       </c>
-      <c r="E28" s="8"/>
+      <c r="E28" s="10"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
       <c r="C29" s="1">
         <v>6</v>
       </c>
       <c r="D29" s="3">
         <v>2.32727791187156E-3</v>
       </c>
-      <c r="E29" s="8"/>
+      <c r="E29" s="10"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
       <c r="C30" s="1">
         <v>7</v>
       </c>
       <c r="D30" s="3">
         <v>3.3527282363668498E-3</v>
       </c>
-      <c r="E30" s="8"/>
+      <c r="E30" s="10"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
       <c r="C31" s="1">
         <v>8</v>
       </c>
       <c r="D31" s="3">
         <v>2.00939520752292E-3</v>
       </c>
-      <c r="E31" s="8"/>
+      <c r="E31" s="10"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
       <c r="C32" s="1">
         <v>9</v>
       </c>
       <c r="D32" s="3">
         <v>2.9226176336739399E-3</v>
       </c>
-      <c r="E32" s="8"/>
+      <c r="E32" s="10"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
       <c r="C33" s="1">
         <v>10</v>
       </c>
       <c r="D33" s="3">
         <v>2.3055594287943698E-3</v>
       </c>
-      <c r="E33" s="8"/>
+      <c r="E33" s="10"/>
       <c r="G33" s="4">
         <v>2.3055594287943698E-3</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A2:A33"/>
+    <mergeCell ref="B2:B12"/>
+    <mergeCell ref="E2:E12"/>
+    <mergeCell ref="B13:B23"/>
+    <mergeCell ref="E13:E23"/>
+    <mergeCell ref="B24:B33"/>
+    <mergeCell ref="E24:E33"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{905FDE81-1C1B-4B15-90FD-7441C7029F15}">
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.77734375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="22.77734375" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="11">
+        <f>AVERAGE(D2:D12)</f>
+        <v>2.8999263001501983E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="7">
+        <v>2.9086299843656201E-3</v>
+      </c>
+      <c r="E3" s="10"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="7">
+        <v>2.8725109233065098E-3</v>
+      </c>
+      <c r="E4" s="10"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="10"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="10"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="1">
+        <v>6</v>
+      </c>
+      <c r="D7" s="7">
+        <v>2.9094927500167801E-3</v>
+      </c>
+      <c r="E7" s="10"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="1">
+        <v>7</v>
+      </c>
+      <c r="D8" s="7">
+        <v>2.9300338678111201E-3</v>
+      </c>
+      <c r="E8" s="10"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="1">
+        <v>8</v>
+      </c>
+      <c r="D9" s="7">
+        <v>2.8954508177678399E-3</v>
+      </c>
+      <c r="E9" s="10"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="1">
+        <v>9</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="10"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="1">
+        <v>10</v>
+      </c>
+      <c r="D11" s="7">
+        <v>2.8834394576333199E-3</v>
+      </c>
+      <c r="E11" s="10"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="1">
+        <v>11</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="10"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="11">
+        <f>AVERAGE(D13:D23)</f>
+        <v>2.6829958775808596E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="1">
+        <v>2</v>
+      </c>
+      <c r="D14" s="7">
+        <v>2.6282434237133502E-3</v>
+      </c>
+      <c r="E14" s="10"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="1">
+        <v>3</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="10"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="1">
+        <v>4</v>
+      </c>
+      <c r="D16" s="7">
+        <v>2.7524372879068298E-3</v>
+      </c>
+      <c r="E16" s="10"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="1">
+        <v>5</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="10"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="1">
+        <v>6</v>
+      </c>
+      <c r="D18" s="7">
+        <v>2.5237854282296E-3</v>
+      </c>
+      <c r="E18" s="10"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="1">
+        <v>7</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="10"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="1">
+        <v>8</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="10"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="1">
+        <v>9</v>
+      </c>
+      <c r="D21" s="7">
+        <v>2.6816447983030599E-3</v>
+      </c>
+      <c r="E21" s="10"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="1">
+        <v>10</v>
+      </c>
+      <c r="D22" s="7">
+        <v>2.7565596821078398E-3</v>
+      </c>
+      <c r="E22" s="10"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="1">
+        <v>11</v>
+      </c>
+      <c r="D23" s="7">
+        <v>2.7553046452244798E-3</v>
+      </c>
+      <c r="E23" s="10"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="11">
+        <f>AVERAGE(D24:D33)</f>
+        <v>2.1463692199712816E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="1">
+        <v>2</v>
+      </c>
+      <c r="D25" s="6">
+        <v>2.0223762558382102E-3</v>
+      </c>
+      <c r="E25" s="10"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="1">
+        <v>3</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="10"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="1">
+        <v>4</v>
+      </c>
+      <c r="D27" s="6">
+        <v>2.1925517311301699E-3</v>
+      </c>
+      <c r="E27" s="10"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="1">
+        <v>5</v>
+      </c>
+      <c r="D28" s="6">
+        <v>2.0210547846704601E-3</v>
+      </c>
+      <c r="E28" s="10"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="1">
+        <v>6</v>
+      </c>
+      <c r="D29" s="6">
+        <v>2.32727791187156E-3</v>
+      </c>
+      <c r="E29" s="10"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="1">
+        <v>7</v>
+      </c>
+      <c r="D30" s="3"/>
+      <c r="E30" s="10"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="1">
+        <v>8</v>
+      </c>
+      <c r="D31" s="6">
+        <v>2.00939520752292E-3</v>
+      </c>
+      <c r="E31" s="10"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="1">
+        <v>9</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="10"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="1">
+        <v>10</v>
+      </c>
+      <c r="D33" s="6">
+        <v>2.3055594287943698E-3</v>
+      </c>
+      <c r="E33" s="10"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="8">
